--- a/docs/rag_run_guide_rev1.xlsx
+++ b/docs/rag_run_guide_rev1.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_노트북_상세" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4_설정_기입" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5_안돌리는_파일" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6_소스유형_수정" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -661,7 +662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -841,7 +842,19 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>라이브러리 13개 역할 — 직접 실행하지 않음</t>
+          <t>라이브러리 14개 역할 — 직접 실행하지 않음</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>6_소스유형_수정</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>★ 소스 카테고리 추가 · 이름 변경 · 흡수 · 기준 변경하는 법</t>
         </is>
       </c>
     </row>
@@ -1993,7 +2006,7 @@
         </is>
       </c>
       <c r="D5" s="23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E5" s="22" t="inlineStr">
         <is>
@@ -3007,7 +3020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3267,6 +3280,23 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="28" t="inlineStr">
+        <is>
+          <t>lab_sources.py</t>
+        </is>
+      </c>
+      <c r="B18" s="29" t="inlineStr">
+        <is>
+          <t>★ 소스 유형 정의 — 이름 · 필수 메타 · 정제 규칙 · 청킹 기본값</t>
+        </is>
+      </c>
+      <c r="C18" s="30" t="inlineStr">
+        <is>
+          <t>★ 수정함</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:C1"/>
@@ -3275,4 +3305,363 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>6. 소스 유형(카테고리) 수정 방법</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>유형 정의는 lab_sources.py 한 곳 · 사내 코드 연결은 lab_config.DOC_TYPE_MAP 한 곳</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>상황</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>어디를 고치나</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>무엇을 쓰나</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>예시</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>확인 방법</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>새 유형 추가 (예: SNS)</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>lab_sources.py → SOURCES</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>SOURCES 에 항목 추가 (SNS 예시가 주석으로 들어 있음 — 해제만 하면 됨)</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>'SNS': dict(ko='SNS', group='외부', security=0, required=['org_name'],
+  clean=dict(noise=[r'^RT\s@\S+', r'https?://\S+']), chunk=dict(size=280))</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>nb00 [1b] 셀에서 표에 보이는지</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>사내 코드가 다름</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>lab_config.py → DOC_TYPE_MAP</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>왼쪽에 사내 코드, 오른쪽에 표준 코드</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>'SEC_RPT': 'BROKER'</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>nb00 [1b] 상태 = 정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>표기 이름만 변경</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>lab_sources.py → SOURCES[코드]['ko']</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>코드는 그대로 두고 이름만</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>SOURCES['BROKER']['ko'] = '리서치'</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>모든 표 · 도식 표기가 바뀜</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>쓰지 않는 유형</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>lab_sources.py → enabled</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>False 로 두면 점검 · 통계에서 제외 (정의는 남김)</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>SOURCES['MEETING']['enabled'] = False</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>nb00 [1b] 사용 열 = X</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>다른 유형에 흡수</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>lab_config.py → DOC_TYPE_MAP</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>사내 코드를 흡수할 표준 코드로 매핑</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>'MOM': 'EMAIL'  (회의록을 메일로)</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>nb00 [1b] 매핑_결과 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>필수 메타 기준 변경</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>lab_sources.py → required</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>유형별 추가 필수 항목 (공통 title · published_at 은 자동)</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>SOURCES['NEWS']['required'] = ['org_name', 'src_url']</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>nb00 [4] 메타 충족률 표</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>정제 규칙 추가</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>lab_sources.py → clean.noise</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>정규식 목록 · email(인용·서명 제거) · repeated(반복 머리글)</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>noise=[r'^\[속보\]', r'^사진=.*']</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>nb02 노이즈 잔존율</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>청크 크기 변경</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>lab_sources.py → chunk</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>size = 목표 글자 수 · table = 표를 별도 청크로</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>chunk=dict(size=350, table=True)</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>nb02 길이 분포 · nb06 Recall</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>보안 등급 변경</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>lab_sources.py → security</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0~3 · 권한 필터에 사용</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>security=3</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>nb01 · 권한 점검</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>원칙</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>유형 정의(이름 · 필수 메타 · 정제 · 청킹)는 lab_sources.py 한 곳 / 사내 코드 연결은 lab_config.DOC_TYPE_MAP 한 곳. 다른 파일은 고치지 않는다.</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="n"/>
+      <c r="D15" s="14" t="n"/>
+      <c r="E15" s="15" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>반드시 확인</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>nb00 [1b] 셀 — 미정의 코드가 있으면 그 유형은 필수 메타 · 정제 규칙이 적용되지 않은 채 통과한다.</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="n"/>
+      <c r="D16" s="14" t="n"/>
+      <c r="E16" s="15" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>수정 후</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>Spyder 에서 [0] 준비 셀을 다시 실행해야 변경이 반영된다 (importlib.reload 포함).</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="n"/>
+      <c r="D17" s="14" t="n"/>
+      <c r="E17" s="15" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/docs/rag_run_guide_rev1.xlsx
+++ b/docs/rag_run_guide_rev1.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_노트북_상세" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4_설정_기입" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5_안돌리는_파일" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6_소스유형_수정" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6_소스카테고리_수정" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -849,12 +849,12 @@
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>6_소스유형_수정</t>
+          <t>6_소스카테고리_수정</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>★ 소스 카테고리 추가 · 이름 변경 · 흡수 · 기준 변경하는 법</t>
+          <t>★ 카테고리 추가 · 제거 · 이름 변경 · 사내 코드 대응</t>
         </is>
       </c>
     </row>
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="D7" s="23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E7" s="22" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
       </c>
       <c r="B18" s="29" t="inlineStr">
         <is>
-          <t>★ 소스 유형 정의 — 이름 · 필수 메타 · 정제 규칙 · 청킹 기본값</t>
+          <t>★ 소스 카테고리 정의 — 코드 · 이름 · 사내 DB 값 · 필수 메타 · 정제 · 청킹</t>
         </is>
       </c>
       <c r="C18" s="30" t="inlineStr">
@@ -3313,134 +3313,113 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="52" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>6. 소스 유형(카테고리) 수정 방법</t>
+          <t>6. 소스 카테고리 추가 · 제거 · 이름 변경</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>유형 정의는 lab_sources.py 한 곳 · 사내 코드 연결은 lab_config.DOC_TYPE_MAP 한 곳</t>
+          <t>lab_sources.py 의 SOURCES 딕셔너리 한 곳 — 한 줄이 한 카테고리</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>상황</t>
+          <t>하고 싶은 것</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>어디를 고치나</t>
+          <t>어떻게</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>무엇을 쓰나</t>
+          <t>예시</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>예시</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>확인 방법</t>
+          <t>확인</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>새 유형 추가 (예: SNS)</t>
+          <t>추가</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>lab_sources.py → SOURCES</t>
+          <t>SOURCES 에 항목 한 줄 추가</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>SOURCES 에 항목 추가 (SNS 예시가 주석으로 들어 있음 — 해제만 하면 됨)</t>
+          <t>'SNS': dict(ko='SNS', alias=['SNS', 'SNS_POST'], group='외부',
+            required=['org_name'], noise=[r'^RT\s@\S+'], chunk=280)</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>'SNS': dict(ko='SNS', group='외부', security=0, required=['org_name'],
-  clean=dict(noise=[r'^RT\s@\S+', r'https?://\S+']), chunk=dict(size=280))</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>nb00 [1b] 셀에서 표에 보이는지</t>
+          <t>nb00 [1b] 정의 표에 나타남</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>사내 코드가 다름</t>
+          <t>제거</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>lab_config.py → DOC_TYPE_MAP</t>
+          <t>그 항목 줄을 지움</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>왼쪽에 사내 코드, 오른쪽에 표준 코드</t>
+          <t>'MEETING': dict(...) 줄 삭제</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>'SEC_RPT': 'BROKER'</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>nb00 [1b] 상태 = 정상</t>
+          <t>nb00 [1b] 에서 해당 코드가 "정의 없음"</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>표기 이름만 변경</t>
+          <t>이름 변경</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>lab_sources.py → SOURCES[코드]['ko']</t>
+          <t>ko 값을 고침</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>코드는 그대로 두고 이름만</t>
+          <t>SOURCES['BROKER']['ko'] = '리서치'</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>SOURCES['BROKER']['ko'] = '리서치'</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>모든 표 · 도식 표기가 바뀜</t>
         </is>
@@ -3449,81 +3428,66 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>쓰지 않는 유형</t>
+          <t>사내 DB 값 대응</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>lab_sources.py → enabled</t>
+          <t>alias 목록에 넣고 뺌</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>False 로 두면 점검 · 통계에서 제외 (정의는 남김)</t>
+          <t>SOURCES['NEWS']['alias'] = ['NEWS', '뉴스', 'NEWS_EN']</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>SOURCES['MEETING']['enabled'] = False</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>nb00 [1b] 사용 열 = X</t>
+          <t>nb00 [1b] 상태 = 정상</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>다른 유형에 흡수</t>
+          <t>두 코드를 하나로</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>lab_config.py → DOC_TYPE_MAP</t>
+          <t>한 카테고리의 alias 에 둘 다 적음</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>사내 코드를 흡수할 표준 코드로 매핑</t>
+          <t>SOURCES['EMAIL']['alias'] = ['EMAIL', 'MOM']</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>'MOM': 'EMAIL'  (회의록을 메일로)</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>nb00 [1b] 매핑_결과 확인</t>
+          <t>분포표에서 합쳐져 집계</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>필수 메타 기준 변경</t>
+          <t>필수 메타 변경</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>lab_sources.py → required</t>
+          <t>required 목록 수정 (title · published_at 은 공통이라 자동)</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>유형별 추가 필수 항목 (공통 title · published_at 은 자동)</t>
+          <t>SOURCES['NEWS']['required'] = ['org_name', 'src_url']</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>SOURCES['NEWS']['required'] = ['org_name', 'src_url']</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>nb00 [4] 메타 충족률 표</t>
+          <t>nb00 [4] 메타 충족률</t>
         </is>
       </c>
     </row>
@@ -3535,20 +3499,15 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>lab_sources.py → clean.noise</t>
+          <t>noise 에 정규식 추가 / strip_email · strip_repeat</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>정규식 목록 · email(인용·서명 제거) · repeated(반복 머리글)</t>
+          <t>SOURCES['NEWS']['noise'] += [r'^\[속보\]', r'^사진=.*']</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>noise=[r'^\[속보\]', r'^사진=.*']</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>nb02 노이즈 잔존율</t>
         </is>
@@ -3557,54 +3516,44 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>청크 크기 변경</t>
+          <t>청크 기준 변경</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>lab_sources.py → chunk</t>
+          <t>chunk = 목표 글자 수 · table = 표 분리</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>size = 목표 글자 수 · table = 표를 별도 청크로</t>
+          <t>SOURCES['NEWS']['chunk'] = 300</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>chunk=dict(size=350, table=True)</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>nb02 길이 분포 · nb06 Recall</t>
+          <t>nb02 [+] 기준 적용 시 비교</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>보안 등급 변경</t>
+          <t>보안 등급</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>lab_sources.py → security</t>
+          <t>security 0~3</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>0~3 · 권한 필터에 사용</t>
+          <t>SOURCES['EXEC_REPORT']['security'] = 3</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>security=3</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>nb01 · 권한 점검</t>
+          <t>권한 점검</t>
         </is>
       </c>
     </row>
@@ -3616,12 +3565,11 @@
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>유형 정의(이름 · 필수 메타 · 정제 · 청킹)는 lab_sources.py 한 곳 / 사내 코드 연결은 lab_config.DOC_TYPE_MAP 한 곳. 다른 파일은 고치지 않는다.</t>
+          <t>카테고리에 관한 모든 것이 SOURCES 한 곳에 있다. lab_config 는 접속 · 테이블 설정만 담당한다.</t>
         </is>
       </c>
       <c r="C15" s="14" t="n"/>
-      <c r="D15" s="14" t="n"/>
-      <c r="E15" s="15" t="n"/>
+      <c r="D15" s="15" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
@@ -3631,12 +3579,11 @@
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>nb00 [1b] 셀 — 미정의 코드가 있으면 그 유형은 필수 메타 · 정제 규칙이 적용되지 않은 채 통과한다.</t>
+          <t>nb00 [1b] — 정의에 없는 코드는 필수 메타 · 정제 규칙이 적용되지 않은 채 통과한다.</t>
         </is>
       </c>
       <c r="C16" s="14" t="n"/>
-      <c r="D16" s="14" t="n"/>
-      <c r="E16" s="15" t="n"/>
+      <c r="D16" s="15" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
@@ -3646,20 +3593,19 @@
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>Spyder 에서 [0] 준비 셀을 다시 실행해야 변경이 반영된다 (importlib.reload 포함).</t>
+          <t>Spyder 에서 [0] 준비 셀을 다시 실행해야 반영된다.</t>
         </is>
       </c>
       <c r="C17" s="14" t="n"/>
-      <c r="D17" s="14" t="n"/>
-      <c r="E17" s="15" t="n"/>
+      <c r="D17" s="15" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B16:D16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>

--- a/docs/rag_run_guide_rev1.xlsx
+++ b/docs/rag_run_guide_rev1.xlsx
@@ -1924,12 +1924,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -1943,7 +1943,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>구분 — 핵심: 반드시 / 선택: 필요할 때 / 참고: 이해용</t>
+          <t>구분 — 핵심: 반드시 / 선택: 필요할 때 / 참고: 이해용 · 체크리스트 = docs/rag_checklist_rev10.xlsx</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>입력(무엇을 읽나)</t>
+          <t>체크리스트 위치</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="E5" s="22" t="inlineStr">
         <is>
-          <t>문서 · 청크 테이블</t>
+          <t>[단계별_실행도구] S00 · [P1_적재공통]</t>
         </is>
       </c>
       <c r="F5" s="22" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>문서 테이블</t>
+          <t>[P1_적재공통] S01 · S05</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="E7" s="22" t="inlineStr">
         <is>
-          <t>문서 · 청크</t>
+          <t>[P1_적재공통] S02 · S03 · S04</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>청크 · 골든셋</t>
+          <t>[P1_검색] S09</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Milvus · 청크</t>
+          <t>[P1_적재공통] S06 · [P1_검색] S10</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>golden/smoke20.csv</t>
+          <t>[P1_검색] S07 · [스모크20]</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="E11" s="22" t="inlineStr">
         <is>
-          <t>골든셋 · 청크</t>
+          <t>[P1_검색] S09~S12 · S15</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>지표 정의서 · SQL 골든셋</t>
+          <t>[P3_정형연계] S22~S29</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>문서 · 청크</t>
+          <t>[P1_검색] S15</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="E14" s="25" t="inlineStr">
         <is>
-          <t>자동 평가셋</t>
+          <t>체크리스트 없음 — 평가팩 엑셀 연계</t>
         </is>
       </c>
       <c r="F14" s="25" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="E15" s="22" t="inlineStr">
         <is>
-          <t>골든셋 · 청크 · LLM</t>
+          <t>[P1_검색] S14 · S15</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>사외 60문항 · 청크</t>
+          <t>체크리스트 없음 — 평가팩 2d · 2e</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="E17" s="22" t="inlineStr">
         <is>
-          <t>청크 · LLM</t>
+          <t>[P1_검색] S15</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="E18" s="22" t="inlineStr">
         <is>
-          <t>골든셋 · 청크 · LLM</t>
+          <t>[P1_검색] S08 · S11 · S12 · S14</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
